--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10711"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Training material\DemoS_012\SubRES_TMPL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/billychan/Documents/TIMES Modle/Demo_S012_Vonline/SubRES_TMPL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5461B1E9-0EE1-4767-8258-C2DC237790A8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A14D9074-ABF7-E64D-A0E1-679605A2C08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" activeTab="4"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="27760" windowHeight="17140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC" sheetId="4" r:id="rId1"/>
@@ -27,26 +27,18 @@
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Gary Goldstein</author>
     <author>Amit Kanudia</author>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="K3" authorId="0" shapeId="0">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -160,7 +152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="1" shapeId="0">
+    <comment ref="P3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -186,7 +178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="2" shapeId="0">
+    <comment ref="Q3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -259,7 +251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="2" shapeId="0">
+    <comment ref="R3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -312,7 +304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="2" shapeId="0">
+    <comment ref="S3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
         <r>
           <rPr>
@@ -345,7 +337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I8" authorId="2" shapeId="0">
+    <comment ref="I8" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <r>
           <rPr>
@@ -392,7 +384,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q8" authorId="2" shapeId="0">
+    <comment ref="Q8" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
@@ -485,7 +477,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R8" authorId="1" shapeId="0">
+    <comment ref="R8" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
@@ -510,7 +502,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S8" authorId="2" shapeId="0">
+    <comment ref="S8" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
@@ -573,7 +565,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K9" authorId="2" shapeId="0">
+    <comment ref="K9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -821,12 +813,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="I15" authorId="0" shapeId="0">
+    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -850,7 +842,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J15" authorId="0" shapeId="0">
+    <comment ref="J15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -864,7 +856,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I16" authorId="0" shapeId="0">
+    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -888,7 +880,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J16" authorId="0" shapeId="0">
+    <comment ref="J16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -902,7 +894,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I17" authorId="0" shapeId="0">
+    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -926,7 +918,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J17" authorId="0" shapeId="0">
+    <comment ref="J17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
@@ -940,7 +932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I18" authorId="0" shapeId="0">
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -964,7 +956,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J18" authorId="0" shapeId="0">
+    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
@@ -978,7 +970,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I19" authorId="0" shapeId="0">
+    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -1002,7 +994,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J19" authorId="0" shapeId="0">
+    <comment ref="J19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -1016,7 +1008,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="0" shapeId="0">
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -1040,7 +1032,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J20" authorId="0" shapeId="0">
+    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -1054,7 +1046,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I27" authorId="0" shapeId="0">
+    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -1078,7 +1070,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0">
+    <comment ref="J27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -1092,7 +1084,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I28" authorId="0" shapeId="0">
+    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -1116,7 +1108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J28" authorId="0" shapeId="0">
+    <comment ref="J28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000010000000}">
       <text>
         <r>
           <rPr>
@@ -1130,7 +1122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I29" authorId="0" shapeId="0">
+    <comment ref="I29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000011000000}">
       <text>
         <r>
           <rPr>
@@ -1154,7 +1146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J29" authorId="0" shapeId="0">
+    <comment ref="J29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000012000000}">
       <text>
         <r>
           <rPr>
@@ -1168,7 +1160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I30" authorId="0" shapeId="0">
+    <comment ref="I30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000013000000}">
       <text>
         <r>
           <rPr>
@@ -1192,7 +1184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J30" authorId="0" shapeId="0">
+    <comment ref="J30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000014000000}">
       <text>
         <r>
           <rPr>
@@ -1206,7 +1198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I31" authorId="0" shapeId="0">
+    <comment ref="I31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000015000000}">
       <text>
         <r>
           <rPr>
@@ -1230,7 +1222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J31" authorId="0" shapeId="0">
+    <comment ref="J31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000016000000}">
       <text>
         <r>
           <rPr>
@@ -1244,7 +1236,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I32" authorId="0" shapeId="0">
+    <comment ref="I32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000017000000}">
       <text>
         <r>
           <rPr>
@@ -1268,7 +1260,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J32" authorId="0" shapeId="0">
+    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000018000000}">
       <text>
         <r>
           <rPr>
@@ -1287,14 +1279,14 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Gary Goldstein</author>
     <author>Amit Kanudia</author>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="N3" authorId="0" shapeId="0">
+    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1408,7 +1400,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="1" shapeId="0">
+    <comment ref="S3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1434,7 +1426,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="2" shapeId="0">
+    <comment ref="T3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
       <text>
         <r>
           <rPr>
@@ -1507,7 +1499,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="2" shapeId="0">
+    <comment ref="U3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
       <text>
         <r>
           <rPr>
@@ -1560,7 +1552,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="2" shapeId="0">
+    <comment ref="V3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
       <text>
         <r>
           <rPr>
@@ -1593,7 +1585,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T9" authorId="2" shapeId="0">
+    <comment ref="T9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
       <text>
         <r>
           <rPr>
@@ -1686,7 +1678,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U9" authorId="1" shapeId="0">
+    <comment ref="U9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
       <text>
         <r>
           <rPr>
@@ -1711,7 +1703,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V9" authorId="2" shapeId="0">
+    <comment ref="V9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
       <text>
         <r>
           <rPr>
@@ -1774,7 +1766,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N10" authorId="2" shapeId="0">
+    <comment ref="N10" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
       <text>
         <r>
           <rPr>
@@ -2798,13 +2790,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="171" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="185" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="186" formatCode="0.000"/>
-    <numFmt numFmtId="187" formatCode="0.0"/>
-    <numFmt numFmtId="214" formatCode="\Te\x\t"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="\Te\x\t"/>
   </numFmts>
   <fonts count="31" x14ac:knownFonts="1">
     <font>
@@ -3178,14 +3170,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="185" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="185" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="185" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
@@ -3383,8 +3375,8 @@
     <xf numFmtId="0" fontId="26" fillId="3" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3426,7 +3418,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -3435,108 +3427,108 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="15" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="214" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="214" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="214" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="214" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="214" fontId="26" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="26" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="214" fontId="26" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="26" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="214" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="214" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="214" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="214" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="214" fontId="16" fillId="0" borderId="0" xfId="35" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="214" fontId="4" fillId="0" borderId="0" xfId="18" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="214" fontId="26" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="35" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="18" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="26" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="214" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="214" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="214" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="214" fontId="26" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="26" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="214" fontId="26" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="26" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="214" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="214" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="214" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="59">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
     <cellStyle name="40% - Accent3" xfId="2" builtinId="39"/>
     <cellStyle name="Accent2" xfId="3" builtinId="33"/>
-    <cellStyle name="calculated" xfId="4"/>
-    <cellStyle name="Calculation 2" xfId="5"/>
-    <cellStyle name="Comma 10" xfId="6"/>
-    <cellStyle name="Comma 11" xfId="7"/>
-    <cellStyle name="Comma 2" xfId="8"/>
-    <cellStyle name="Comma 2 2" xfId="9"/>
-    <cellStyle name="Comma 2 3" xfId="10"/>
-    <cellStyle name="Comma 2 4" xfId="11"/>
-    <cellStyle name="Comma 2 5" xfId="12"/>
-    <cellStyle name="Comma 3" xfId="13"/>
+    <cellStyle name="calculated" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Calculation 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Comma 10" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Comma 11" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Comma 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Comma 2 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Comma 2 3" xfId="10" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Comma 2 4" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Comma 2 5" xfId="12" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Comma 3" xfId="13" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
     <cellStyle name="Good" xfId="14" builtinId="26"/>
     <cellStyle name="Hyperlink" xfId="15" builtinId="8"/>
-    <cellStyle name="Hyperlink 3" xfId="16"/>
+    <cellStyle name="Hyperlink 3" xfId="16" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
     <cellStyle name="Neutral" xfId="17" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="18"/>
-    <cellStyle name="Normal 11" xfId="19"/>
-    <cellStyle name="Normal 11 2" xfId="20"/>
-    <cellStyle name="Normal 11 3" xfId="21"/>
-    <cellStyle name="Normal 11 4" xfId="22"/>
-    <cellStyle name="Normal 12" xfId="23"/>
-    <cellStyle name="Normal 12 2" xfId="24"/>
-    <cellStyle name="Normal 12 3" xfId="25"/>
-    <cellStyle name="Normal 12 4" xfId="26"/>
-    <cellStyle name="Normal 2" xfId="27"/>
-    <cellStyle name="Normal 2 2" xfId="28"/>
-    <cellStyle name="Normal 2 3" xfId="29"/>
-    <cellStyle name="Normal 2 4" xfId="30"/>
-    <cellStyle name="Normal 3" xfId="31"/>
-    <cellStyle name="Normal 39" xfId="32"/>
-    <cellStyle name="Normal 4" xfId="33"/>
-    <cellStyle name="Normal 4 2" xfId="34"/>
-    <cellStyle name="Normal 8" xfId="35"/>
-    <cellStyle name="Normal 9 2" xfId="36"/>
-    <cellStyle name="Normale_B2020" xfId="37"/>
-    <cellStyle name="Note 2" xfId="38"/>
-    <cellStyle name="Percent 2" xfId="39"/>
-    <cellStyle name="Percent 2 2" xfId="40"/>
-    <cellStyle name="Percent 2 2 2" xfId="41"/>
-    <cellStyle name="Percent 2 3" xfId="42"/>
-    <cellStyle name="Percent 3" xfId="43"/>
-    <cellStyle name="Percent 3 2" xfId="44"/>
-    <cellStyle name="Percent 3 2 2" xfId="45"/>
-    <cellStyle name="Percent 3 3" xfId="46"/>
-    <cellStyle name="Percent 3 4" xfId="47"/>
-    <cellStyle name="Percent 4" xfId="48"/>
-    <cellStyle name="Percent 4 2" xfId="49"/>
-    <cellStyle name="Percent 4 3" xfId="50"/>
-    <cellStyle name="Percent 4 4" xfId="51"/>
-    <cellStyle name="Percent 5" xfId="52"/>
-    <cellStyle name="Percent 5 2" xfId="53"/>
-    <cellStyle name="Percent 6" xfId="54"/>
-    <cellStyle name="Percent 6 2" xfId="55"/>
-    <cellStyle name="Percent 7" xfId="56"/>
-    <cellStyle name="Percent 8" xfId="57"/>
-    <cellStyle name="Standard_Sce_D_Extraction" xfId="58"/>
+    <cellStyle name="Normal 10" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Normal 11" xfId="19" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Normal 11 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Normal 11 3" xfId="21" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Normal 11 4" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Normal 12" xfId="23" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Normal 12 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Normal 12 3" xfId="25" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Normal 12 4" xfId="26" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Normal 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Normal 2 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Normal 2 3" xfId="29" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Normal 2 4" xfId="30" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Normal 3" xfId="31" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="Normal 39" xfId="32" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Normal 4" xfId="33" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="Normal 4 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="Normal 8" xfId="35" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="Normal 9 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="Normale_B2020" xfId="37" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Note 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Percent 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="Percent 2 2" xfId="40" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="Percent 2 2 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="Percent 2 3" xfId="42" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="Percent 3" xfId="43" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="Percent 3 2" xfId="44" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="Percent 3 2 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="Percent 3 3" xfId="46" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="Percent 3 4" xfId="47" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="Percent 4" xfId="48" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="Percent 4 2" xfId="49" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Percent 4 3" xfId="50" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Percent 4 4" xfId="51" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="Percent 5" xfId="52" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Percent 5 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Percent 6" xfId="54" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Percent 6 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="Percent 7" xfId="56" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="Percent 8" xfId="57" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="Standard_Sce_D_Extraction" xfId="58" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4873,42 +4865,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y42"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="25" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="25" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" style="25" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" style="25" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="16.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="25" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="25" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.1640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" style="25" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" style="25" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" style="25" customWidth="1"/>
     <col min="12" max="12" width="7" style="25" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15" style="25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5" style="25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="2" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.5703125" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="54.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.5" customWidth="1"/>
+    <col min="18" max="18" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="54.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" customWidth="1"/>
     <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.28515625" customWidth="1"/>
-    <col min="23" max="23" width="12.7109375" customWidth="1"/>
-    <col min="24" max="24" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.33203125" customWidth="1"/>
+    <col min="23" max="23" width="12.6640625" customWidth="1"/>
+    <col min="24" max="24" width="7.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.15">
       <c r="P2" s="58"/>
       <c r="Q2" s="58"/>
       <c r="R2" s="58"/>
@@ -4920,7 +4912,7 @@
       <c r="X2" s="58"/>
       <c r="Y2" s="54"/>
     </row>
-    <row r="3" spans="1:25" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="B3" s="24" t="s">
         <v>43</v>
       </c>
@@ -4943,7 +4935,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="B4" s="11" t="s">
         <v>49</v>
       </c>
@@ -4977,7 +4969,7 @@
       <c r="W4" s="109"/>
       <c r="X4" s="109"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.15">
       <c r="P5" s="110" t="s">
         <v>8</v>
       </c>
@@ -5006,7 +4998,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="26" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26"/>
       <c r="B6" s="34" t="s">
         <v>57</v>
@@ -5058,7 +5050,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="26"/>
       <c r="B7" s="33" t="s">
         <v>66</v>
@@ -5092,11 +5084,11 @@
       <c r="W7" s="9"/>
       <c r="X7" s="9"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.15">
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.15">
       <c r="E10" s="6" t="s">
         <v>0</v>
       </c>
@@ -5119,7 +5111,7 @@
       <c r="W10" s="109"/>
       <c r="X10" s="109"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="14" x14ac:dyDescent="0.15">
       <c r="B11" s="14" t="s">
         <v>1</v>
       </c>
@@ -5188,7 +5180,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="24" x14ac:dyDescent="0.15">
       <c r="B12" s="13" t="s">
         <v>73</v>
       </c>
@@ -5253,7 +5245,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B13" s="12" t="s">
         <v>80</v>
       </c>
@@ -5292,7 +5284,7 @@
       <c r="W13" s="112"/>
       <c r="X13" s="112"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.15">
       <c r="B14" s="25" t="str">
         <f>R14</f>
         <v>ELCTNCOA01</v>
@@ -5352,7 +5344,7 @@
       <c r="W14" s="114"/>
       <c r="X14" s="114"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.15">
       <c r="B15" s="25" t="str">
         <f>R15</f>
         <v>ELCTNOIL01</v>
@@ -5408,7 +5400,7 @@
       <c r="W15" s="116"/>
       <c r="X15" s="116"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.15">
       <c r="B16" s="25" t="str">
         <f>R16</f>
         <v>ELCTNGAS01</v>
@@ -5469,7 +5461,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.15">
       <c r="E17" s="25">
         <v>2010</v>
       </c>
@@ -5498,7 +5490,7 @@
       <c r="W17" s="114"/>
       <c r="X17" s="114"/>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.15">
       <c r="E18" s="25">
         <v>2015</v>
       </c>
@@ -5527,7 +5519,7 @@
       <c r="W18" s="114"/>
       <c r="X18" s="114"/>
     </row>
-    <row r="19" spans="2:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E19" s="25">
         <v>2020</v>
       </c>
@@ -5556,7 +5548,7 @@
       <c r="W19" s="114"/>
       <c r="X19" s="114"/>
     </row>
-    <row r="20" spans="2:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>249</v>
       </c>
@@ -5612,7 +5604,7 @@
       <c r="W20" s="114"/>
       <c r="X20" s="114"/>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="str">
         <f>R17</f>
         <v>ELCRNBIO01</v>
@@ -5672,7 +5664,7 @@
       <c r="W21" s="114"/>
       <c r="X21" s="114"/>
     </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:24" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="str">
         <f>R18</f>
         <v>ELCRNHYD01</v>
@@ -5718,7 +5710,7 @@
       <c r="U22" s="8"/>
       <c r="V22" s="9"/>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="str">
         <f>R19</f>
         <v>ELCRNWIN01</v>
@@ -5739,7 +5731,8 @@
         <v>0.35</v>
       </c>
       <c r="I23" s="25">
-        <v>1500</v>
+        <f>1500*1.25</f>
+        <v>1875</v>
       </c>
       <c r="J23" s="25">
         <v>35</v>
@@ -5766,7 +5759,7 @@
       <c r="W23" s="8"/>
       <c r="X23" s="8"/>
     </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:24" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="str">
         <f>R20</f>
         <v>ELCRNSOL01</v>
@@ -5812,7 +5805,7 @@
       <c r="W24" s="8"/>
       <c r="X24" s="8"/>
     </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:24" x14ac:dyDescent="0.15">
       <c r="B25" s="27"/>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
@@ -5828,10 +5821,10 @@
       <c r="W25" s="8"/>
       <c r="X25" s="8"/>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B41" s="27"/>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B42" s="27"/>
     </row>
   </sheetData>
@@ -5844,41 +5837,41 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y41"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="25" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="25" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" style="25" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="25" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" style="25" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="25" customWidth="1"/>
+    <col min="2" max="2" width="16.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="25" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="25" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.1640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" style="25" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" style="25" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" style="25" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" style="25" customWidth="1"/>
     <col min="13" max="13" width="15" style="25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5" style="25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="2" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" customWidth="1"/>
-    <col min="17" max="17" width="7.5703125" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="54.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" customWidth="1"/>
-    <col min="21" max="21" width="11.42578125" customWidth="1"/>
-    <col min="22" max="22" width="13.28515625" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" customWidth="1"/>
-    <col min="24" max="24" width="8.140625" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" customWidth="1"/>
+    <col min="17" max="17" width="7.5" customWidth="1"/>
+    <col min="18" max="18" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="54.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" customWidth="1"/>
+    <col min="21" max="21" width="11.5" customWidth="1"/>
+    <col min="22" max="22" width="13.33203125" customWidth="1"/>
+    <col min="23" max="23" width="14.1640625" customWidth="1"/>
+    <col min="24" max="24" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.15">
       <c r="P2" s="58"/>
       <c r="Q2" s="58"/>
       <c r="R2" s="58"/>
@@ -5890,7 +5883,7 @@
       <c r="X2" s="58"/>
       <c r="Y2" s="54"/>
     </row>
-    <row r="3" spans="1:25" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="B3" s="24" t="s">
         <v>43</v>
       </c>
@@ -5913,7 +5906,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="34" x14ac:dyDescent="0.2">
       <c r="B4" s="51" t="s">
         <v>123</v>
       </c>
@@ -5948,7 +5941,7 @@
       <c r="W4" s="109"/>
       <c r="X4" s="109"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.15">
       <c r="P5" s="110" t="s">
         <v>8</v>
       </c>
@@ -5977,7 +5970,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="26" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26"/>
       <c r="B6" s="34"/>
       <c r="C6" s="56"/>
@@ -6019,7 +6012,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="26"/>
       <c r="B7" s="33"/>
       <c r="C7" s="50"/>
@@ -6043,11 +6036,11 @@
       <c r="W7" s="9"/>
       <c r="X7" s="9"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.15">
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.15">
       <c r="E10" s="6" t="s">
         <v>0</v>
       </c>
@@ -6070,7 +6063,7 @@
       <c r="W10" s="109"/>
       <c r="X10" s="109"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="14" x14ac:dyDescent="0.15">
       <c r="B11" s="14" t="s">
         <v>1</v>
       </c>
@@ -6139,7 +6132,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="24" x14ac:dyDescent="0.15">
       <c r="B12" s="73" t="s">
         <v>73</v>
       </c>
@@ -6204,7 +6197,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B13" s="72" t="s">
         <v>80</v>
       </c>
@@ -6243,7 +6236,7 @@
       <c r="W13" s="112"/>
       <c r="X13" s="112"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.15">
       <c r="F14" s="30"/>
       <c r="G14" s="31"/>
       <c r="H14" s="31"/>
@@ -6260,7 +6253,7 @@
       <c r="W14" s="8"/>
       <c r="X14" s="8"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.15">
       <c r="G15" s="31"/>
       <c r="H15" s="31"/>
       <c r="I15" s="27"/>
@@ -6277,7 +6270,7 @@
       <c r="W15" s="8"/>
       <c r="X15" s="8"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.15">
       <c r="G16" s="31"/>
       <c r="H16" s="31"/>
       <c r="J16" s="31"/>
@@ -6293,7 +6286,7 @@
       <c r="W16" s="8"/>
       <c r="X16" s="8"/>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.15">
       <c r="G17" s="31"/>
       <c r="H17" s="31"/>
       <c r="J17" s="31"/>
@@ -6309,7 +6302,7 @@
       <c r="W17" s="8"/>
       <c r="X17" s="8"/>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.15">
       <c r="G18" s="31"/>
       <c r="H18" s="31"/>
       <c r="J18" s="31"/>
@@ -6320,7 +6313,7 @@
       <c r="W18" s="8"/>
       <c r="X18" s="8"/>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.15">
       <c r="G19" s="31"/>
       <c r="H19" s="31"/>
       <c r="J19" s="31"/>
@@ -6331,7 +6324,7 @@
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.15">
       <c r="B20" s="27"/>
       <c r="G20" s="31"/>
       <c r="H20" s="31"/>
@@ -6342,7 +6335,7 @@
       <c r="W20" s="8"/>
       <c r="X20" s="8"/>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.15">
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
@@ -6353,7 +6346,7 @@
       <c r="W21" s="8"/>
       <c r="X21" s="8"/>
     </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:24" x14ac:dyDescent="0.15">
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
@@ -6364,7 +6357,7 @@
       <c r="W22" s="8"/>
       <c r="X22" s="8"/>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.15">
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
@@ -6375,7 +6368,7 @@
       <c r="W23" s="8"/>
       <c r="X23" s="8"/>
     </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:24" x14ac:dyDescent="0.15">
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
@@ -6386,10 +6379,10 @@
       <c r="W24" s="8"/>
       <c r="X24" s="8"/>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B40" s="27"/>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B41" s="27"/>
     </row>
   </sheetData>
@@ -6398,33 +6391,33 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S31"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" customWidth="1"/>
+    <col min="12" max="12" width="7.1640625" customWidth="1"/>
+    <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" customWidth="1"/>
+    <col min="18" max="18" width="15.1640625" customWidth="1"/>
     <col min="19" max="19" width="10" customWidth="1"/>
-    <col min="20" max="16384" width="8.85546875" style="25"/>
+    <col min="20" max="16384" width="8.83203125" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="B1" s="24" t="s">
         <v>43</v>
       </c>
@@ -6442,7 +6435,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="B2" s="51"/>
       <c r="C2" s="51"/>
       <c r="D2" s="51"/>
@@ -6464,7 +6457,7 @@
       <c r="R2" s="109"/>
       <c r="S2" s="109"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
       <c r="K3" s="110" t="s">
         <v>8</v>
       </c>
@@ -6493,7 +6486,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C4" s="2"/>
       <c r="K4" s="112" t="s">
         <v>62</v>
@@ -6523,7 +6516,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.15">
       <c r="K5" s="9"/>
       <c r="L5" s="8"/>
       <c r="M5" s="9"/>
@@ -6534,7 +6527,7 @@
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.15">
       <c r="F7" s="6" t="s">
         <v>0</v>
       </c>
@@ -6551,7 +6544,7 @@
       <c r="R7" s="116"/>
       <c r="S7" s="116"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="14" x14ac:dyDescent="0.15">
       <c r="B8" s="4" t="s">
         <v>1</v>
       </c>
@@ -6605,7 +6598,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8"/>
       <c r="B9" s="72" t="s">
         <v>73</v>
@@ -6656,7 +6649,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8"/>
       <c r="B10" s="72" t="s">
         <v>80</v>
@@ -6687,7 +6680,7 @@
       <c r="R10" s="120"/>
       <c r="S10" s="120"/>
     </row>
-    <row r="11" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -6708,7 +6701,7 @@
       <c r="R11" s="8"/>
       <c r="S11" s="8"/>
     </row>
-    <row r="12" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -6729,7 +6722,7 @@
       <c r="R12" s="8"/>
       <c r="S12" s="8"/>
     </row>
-    <row r="13" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -6750,7 +6743,7 @@
       <c r="R13" s="8"/>
       <c r="S13" s="8"/>
     </row>
-    <row r="14" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -6771,7 +6764,7 @@
       <c r="R14" s="8"/>
       <c r="S14" s="8"/>
     </row>
-    <row r="15" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -6792,7 +6785,7 @@
       <c r="R15" s="8"/>
       <c r="S15" s="8"/>
     </row>
-    <row r="16" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -6813,7 +6806,7 @@
       <c r="R16" s="8"/>
       <c r="S16" s="8"/>
     </row>
-    <row r="17" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="8"/>
@@ -6834,7 +6827,7 @@
       <c r="R17" s="8"/>
       <c r="S17" s="8"/>
     </row>
-    <row r="18" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -6855,7 +6848,7 @@
       <c r="R18" s="8"/>
       <c r="S18" s="8"/>
     </row>
-    <row r="19" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -6876,7 +6869,7 @@
       <c r="R19" s="8"/>
       <c r="S19" s="8"/>
     </row>
-    <row r="20" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -6897,7 +6890,7 @@
       <c r="R20" s="8"/>
       <c r="S20" s="8"/>
     </row>
-    <row r="21" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -6918,7 +6911,7 @@
       <c r="R21" s="8"/>
       <c r="S21" s="8"/>
     </row>
-    <row r="22" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="8"/>
@@ -6939,7 +6932,7 @@
       <c r="R22" s="8"/>
       <c r="S22" s="8"/>
     </row>
-    <row r="23" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -6960,7 +6953,7 @@
       <c r="R23" s="8"/>
       <c r="S23" s="8"/>
     </row>
-    <row r="24" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -6981,7 +6974,7 @@
       <c r="R24" s="8"/>
       <c r="S24" s="8"/>
     </row>
-    <row r="25" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8"/>
       <c r="B25" s="80"/>
       <c r="C25" s="9"/>
@@ -7002,7 +6995,7 @@
       <c r="R25" s="8"/>
       <c r="S25" s="8"/>
     </row>
-    <row r="26" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9"/>
@@ -7023,7 +7016,7 @@
       <c r="R26" s="8"/>
       <c r="S26" s="8"/>
     </row>
-    <row r="27" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -7044,16 +7037,16 @@
       <c r="R27" s="8"/>
       <c r="S27" s="8"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A28" s="8"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A29" s="8"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A30" s="8"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A31" s="8"/>
     </row>
   </sheetData>
@@ -7063,39 +7056,39 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:U48"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" customWidth="1"/>
     <col min="12" max="12" width="2" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="7.140625" customWidth="1"/>
+    <col min="14" max="14" width="7.1640625" customWidth="1"/>
     <col min="15" max="15" width="13" customWidth="1"/>
     <col min="16" max="16" width="75" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.42578125" customWidth="1"/>
-    <col min="18" max="18" width="11.140625" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" customWidth="1"/>
-    <col min="20" max="20" width="13.85546875" customWidth="1"/>
-    <col min="21" max="21" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="6.5" customWidth="1"/>
+    <col min="18" max="18" width="11.1640625" customWidth="1"/>
+    <col min="19" max="19" width="13.5" customWidth="1"/>
+    <col min="20" max="20" width="13.83203125" customWidth="1"/>
+    <col min="21" max="21" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" ht="23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B3" s="38" t="s">
         <v>43</v>
       </c>
@@ -7118,7 +7111,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="17" x14ac:dyDescent="0.2">
       <c r="B4" s="40" t="s">
         <v>133</v>
       </c>
@@ -7141,7 +7134,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="17" x14ac:dyDescent="0.2">
       <c r="B5" s="51" t="s">
         <v>134</v>
       </c>
@@ -7175,7 +7168,7 @@
       <c r="T5" s="109"/>
       <c r="U5" s="109"/>
     </row>
-    <row r="6" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
       <c r="B6" s="51" t="s">
         <v>92</v>
@@ -7228,7 +7221,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="26" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
       <c r="B7" s="39"/>
       <c r="C7" s="39"/>
@@ -7269,7 +7262,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="8"/>
       <c r="B8" s="50"/>
       <c r="C8" s="50"/>
@@ -7292,7 +7285,7 @@
       <c r="T8" s="9"/>
       <c r="U8" s="9"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.15">
       <c r="D11" s="6" t="s">
         <v>0</v>
       </c>
@@ -7314,7 +7307,7 @@
       <c r="T11" s="116"/>
       <c r="U11" s="116"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="14" t="s">
         <v>1</v>
       </c>
@@ -7373,7 +7366,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B13" s="43" t="s">
         <v>73</v>
       </c>
@@ -7430,7 +7423,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B14" s="42" t="s">
         <v>80</v>
       </c>
@@ -7463,7 +7456,7 @@
       <c r="T14" s="112"/>
       <c r="U14" s="112"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B15" s="35" t="str">
         <f t="shared" ref="B15:B38" si="0">O15</f>
         <v>CSHNCOA1</v>
@@ -7515,7 +7508,7 @@
       <c r="T15" s="114"/>
       <c r="U15" s="114"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B16" s="35" t="str">
         <f t="shared" si="0"/>
         <v>CSHNGAS1</v>
@@ -7565,7 +7558,7 @@
       <c r="T16" s="114"/>
       <c r="U16" s="114"/>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B17" s="35" t="str">
         <f t="shared" si="0"/>
         <v>CSHNOIL1</v>
@@ -7615,7 +7608,7 @@
       <c r="T17" s="114"/>
       <c r="U17" s="114"/>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B18" s="35" t="str">
         <f t="shared" si="0"/>
         <v>CSHNBIO1</v>
@@ -7665,7 +7658,7 @@
       <c r="T18" s="114"/>
       <c r="U18" s="114"/>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B19" s="35" t="str">
         <f>O19</f>
         <v>CSHNSOL1</v>
@@ -7715,7 +7708,7 @@
       <c r="T19" s="114"/>
       <c r="U19" s="114"/>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B20" s="35" t="str">
         <f t="shared" si="0"/>
         <v>CSHNELC1</v>
@@ -7765,7 +7758,7 @@
       <c r="T20" s="114"/>
       <c r="U20" s="114"/>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B21" s="87" t="str">
         <f t="shared" si="0"/>
         <v>CAPNELC1</v>
@@ -7813,7 +7806,7 @@
       <c r="T21" s="114"/>
       <c r="U21" s="114"/>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B22" s="35" t="str">
         <f t="shared" si="0"/>
         <v>COTNCOA1</v>
@@ -7861,7 +7854,7 @@
       <c r="T22" s="114"/>
       <c r="U22" s="114"/>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B23" s="35" t="str">
         <f t="shared" si="0"/>
         <v>COTNGAS1</v>
@@ -7909,7 +7902,7 @@
       <c r="T23" s="114"/>
       <c r="U23" s="114"/>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B24" s="35" t="str">
         <f t="shared" si="0"/>
         <v>COTNOIL1</v>
@@ -7956,7 +7949,7 @@
       <c r="T24" s="114"/>
       <c r="U24" s="114"/>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B25" s="35" t="str">
         <f t="shared" si="0"/>
         <v>COTNBIO1</v>
@@ -8003,7 +7996,7 @@
       <c r="T25" s="114"/>
       <c r="U25" s="114"/>
     </row>
-    <row r="26" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:21" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B26" s="98" t="str">
         <f t="shared" si="0"/>
         <v>COTNELC1</v>
@@ -8051,7 +8044,7 @@
       <c r="T26" s="122"/>
       <c r="U26" s="122"/>
     </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B27" s="35" t="str">
         <f t="shared" si="0"/>
         <v>RSHNCOA1</v>
@@ -8101,7 +8094,7 @@
       <c r="T27" s="116"/>
       <c r="U27" s="116"/>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B28" s="35" t="str">
         <f t="shared" si="0"/>
         <v>RSHNGAS1</v>
@@ -8152,7 +8145,7 @@
       <c r="T28" s="116"/>
       <c r="U28" s="116"/>
     </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B29" s="35" t="str">
         <f t="shared" si="0"/>
         <v>RSHNOIL1</v>
@@ -8203,7 +8196,7 @@
       <c r="T29" s="116"/>
       <c r="U29" s="116"/>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B30" s="35" t="str">
         <f t="shared" si="0"/>
         <v>RSHNBIO1</v>
@@ -8254,7 +8247,7 @@
       <c r="T30" s="116"/>
       <c r="U30" s="116"/>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B31" s="35" t="str">
         <f>O31</f>
         <v>RSHNSOL1</v>
@@ -8305,7 +8298,7 @@
       <c r="T31" s="116"/>
       <c r="U31" s="116"/>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B32" s="35" t="str">
         <f t="shared" si="0"/>
         <v>RSHNELC1</v>
@@ -8356,7 +8349,7 @@
       <c r="T32" s="116"/>
       <c r="U32" s="116"/>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B33" s="87" t="str">
         <f t="shared" si="0"/>
         <v>RAPNELC1</v>
@@ -8405,7 +8398,7 @@
       <c r="T33" s="116"/>
       <c r="U33" s="116"/>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B34" s="35" t="str">
         <f t="shared" si="0"/>
         <v>ROTNCOA1</v>
@@ -8454,7 +8447,7 @@
       <c r="T34" s="116"/>
       <c r="U34" s="116"/>
     </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B35" s="35" t="str">
         <f t="shared" si="0"/>
         <v>ROTNGAS1</v>
@@ -8503,7 +8496,7 @@
       <c r="T35" s="116"/>
       <c r="U35" s="116"/>
     </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B36" s="35" t="str">
         <f t="shared" si="0"/>
         <v>ROTNOIL1</v>
@@ -8551,7 +8544,7 @@
       <c r="T36" s="116"/>
       <c r="U36" s="116"/>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B37" s="35" t="str">
         <f t="shared" si="0"/>
         <v>ROTNBIO1</v>
@@ -8599,7 +8592,7 @@
       <c r="T37" s="116"/>
       <c r="U37" s="116"/>
     </row>
-    <row r="38" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:21" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B38" s="98" t="str">
         <f t="shared" si="0"/>
         <v>ROTNELC1</v>
@@ -8648,7 +8641,7 @@
       <c r="T38" s="116"/>
       <c r="U38" s="116"/>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B39" s="54"/>
       <c r="C39" s="54"/>
       <c r="D39" s="54"/>
@@ -8661,7 +8654,7 @@
       <c r="K39" s="54"/>
       <c r="L39" s="54"/>
     </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B40" s="54"/>
       <c r="C40" s="54"/>
       <c r="D40" s="54"/>
@@ -8674,7 +8667,7 @@
       <c r="K40" s="54"/>
       <c r="L40" s="54"/>
     </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B41" s="54"/>
       <c r="C41" s="54"/>
       <c r="D41" s="54"/>
@@ -8687,7 +8680,7 @@
       <c r="K41" s="54"/>
       <c r="L41" s="54"/>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B42" s="54"/>
       <c r="C42" s="54"/>
       <c r="D42" s="54"/>
@@ -8700,7 +8693,7 @@
       <c r="K42" s="54"/>
       <c r="L42" s="54"/>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B43" s="54"/>
       <c r="C43" s="54"/>
       <c r="D43" s="54"/>
@@ -8713,7 +8706,7 @@
       <c r="K43" s="54"/>
       <c r="L43" s="54"/>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B44" s="54"/>
       <c r="C44" s="54"/>
       <c r="D44" s="54"/>
@@ -8726,7 +8719,7 @@
       <c r="K44" s="54"/>
       <c r="L44" s="54"/>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B45" s="54"/>
       <c r="C45" s="54"/>
       <c r="D45" s="54"/>
@@ -8739,7 +8732,7 @@
       <c r="K45" s="54"/>
       <c r="L45" s="54"/>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B46" s="54"/>
       <c r="C46" s="54"/>
       <c r="D46" s="54"/>
@@ -8752,7 +8745,7 @@
       <c r="K46" s="54"/>
       <c r="L46" s="54"/>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B47" s="54"/>
       <c r="C47" s="54"/>
       <c r="D47" s="54"/>
@@ -8765,7 +8758,7 @@
       <c r="K47" s="54"/>
       <c r="L47" s="54"/>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B48" s="54"/>
       <c r="C48" s="54"/>
       <c r="D48" s="54"/>
@@ -8785,35 +8778,35 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:V25"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="2" style="54" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" customWidth="1"/>
-    <col min="15" max="15" width="7.140625" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="78.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" customWidth="1"/>
+    <col min="15" max="15" width="7.1640625" customWidth="1"/>
+    <col min="16" max="16" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="78.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.6640625" customWidth="1"/>
+    <col min="19" max="19" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:22" ht="15" x14ac:dyDescent="0.2">
       <c r="B1" s="49" t="s">
         <v>43</v>
       </c>
@@ -8837,7 +8830,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="2:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:22" ht="17" x14ac:dyDescent="0.2">
       <c r="B2" s="51" t="s">
         <v>99</v>
       </c>
@@ -8872,7 +8865,7 @@
       <c r="U2" s="109"/>
       <c r="V2" s="109"/>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.15">
       <c r="N3" s="110" t="s">
         <v>8</v>
       </c>
@@ -8901,7 +8894,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:22" s="8" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:22" s="8" customFormat="1" ht="26" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="50"/>
       <c r="C4" s="50"/>
       <c r="D4" s="50"/>
@@ -8936,7 +8929,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:22" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" s="50"/>
       <c r="C5" s="50"/>
       <c r="D5" s="50"/>
@@ -8952,7 +8945,7 @@
       <c r="U5" s="9"/>
       <c r="V5" s="9"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.15">
       <c r="D8" s="6" t="s">
         <v>0</v>
       </c>
@@ -8973,7 +8966,7 @@
       <c r="U8" s="116"/>
       <c r="V8" s="116"/>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:22" ht="14" x14ac:dyDescent="0.15">
       <c r="B9" s="14" t="s">
         <v>1</v>
       </c>
@@ -9036,7 +9029,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="2:22" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" ht="25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B10" s="60" t="s">
         <v>73</v>
       </c>
@@ -9097,7 +9090,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="2:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="59" t="s">
         <v>80</v>
       </c>
@@ -9138,7 +9131,7 @@
       <c r="U11" s="125"/>
       <c r="V11" s="125"/>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.15">
       <c r="B12" t="str">
         <f>P12</f>
         <v>TCANGAS1</v>
@@ -9196,7 +9189,7 @@
       </c>
       <c r="V12" s="114"/>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.15">
       <c r="B13" t="str">
         <f t="shared" ref="B13:B23" si="0">P13</f>
         <v>TCANDSL1</v>
@@ -9252,7 +9245,7 @@
       </c>
       <c r="V13" s="114"/>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.15">
       <c r="B14" t="str">
         <f t="shared" si="0"/>
         <v>TCANLPG1</v>
@@ -9308,7 +9301,7 @@
       </c>
       <c r="V14" s="114"/>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.15">
       <c r="B15" t="str">
         <f t="shared" si="0"/>
         <v>TCANGSL1</v>
@@ -9364,7 +9357,7 @@
       </c>
       <c r="V15" s="114"/>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.15">
       <c r="B16" t="str">
         <f>P16</f>
         <v>TCARNBIO1</v>
@@ -9420,7 +9413,7 @@
       </c>
       <c r="V16" s="114"/>
     </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:22" x14ac:dyDescent="0.15">
       <c r="B17" s="86" t="str">
         <f t="shared" si="0"/>
         <v>TCANELC1</v>
@@ -9476,7 +9469,7 @@
       </c>
       <c r="V17" s="126"/>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:22" x14ac:dyDescent="0.15">
       <c r="B18" t="str">
         <f t="shared" si="0"/>
         <v>TPUNGAS1</v>
@@ -9531,7 +9524,7 @@
       </c>
       <c r="V18" s="114"/>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:22" x14ac:dyDescent="0.15">
       <c r="B19" t="str">
         <f t="shared" si="0"/>
         <v>TPUNDSL1</v>
@@ -9586,7 +9579,7 @@
       </c>
       <c r="V19" s="116"/>
     </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:22" x14ac:dyDescent="0.15">
       <c r="B20" t="str">
         <f t="shared" si="0"/>
         <v>TPUNLPG1</v>
@@ -9641,7 +9634,7 @@
       </c>
       <c r="V20" s="116"/>
     </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:22" x14ac:dyDescent="0.15">
       <c r="B21" t="str">
         <f t="shared" si="0"/>
         <v>TPUNGSL1</v>
@@ -9696,7 +9689,7 @@
       </c>
       <c r="V21" s="116"/>
     </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:22" x14ac:dyDescent="0.15">
       <c r="B22" t="str">
         <f>P22</f>
         <v>TPUBNBIO1</v>
@@ -9751,7 +9744,7 @@
       </c>
       <c r="V22" s="116"/>
     </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:22" x14ac:dyDescent="0.15">
       <c r="B23" t="str">
         <f t="shared" si="0"/>
         <v>TPUNELC1</v>
@@ -9806,7 +9799,7 @@
       </c>
       <c r="V23" s="116"/>
     </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:22" x14ac:dyDescent="0.15">
       <c r="F25" s="67"/>
     </row>
   </sheetData>
@@ -9817,24 +9810,24 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="B2:AC2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" style="106" bestFit="1" customWidth="1"/>
-    <col min="2" max="12" width="9.140625" style="106"/>
+    <col min="2" max="12" width="9.1640625" style="106"/>
     <col min="13" max="13" width="5" style="106" customWidth="1"/>
     <col min="14" max="15" width="2" style="106" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="9.140625" style="106"/>
+    <col min="16" max="26" width="9.1640625" style="106"/>
     <col min="27" max="27" width="2" style="106" customWidth="1"/>
-    <col min="28" max="28" width="2.28515625" style="106" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="106"/>
+    <col min="28" max="28" width="2.33203125" style="106" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.1640625" style="106"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B2" s="107" t="s">
         <v>204</v>
       </c>
@@ -9847,9 +9840,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
-    <hyperlink ref="P2" r:id="rId2"/>
-    <hyperlink ref="AC2" r:id="rId3"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="P2" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="AC2" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId4"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/billychan/Documents/TIMES Modle/Demo_S012_Vonline/SubRES_TMPL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A14D9074-ABF7-E64D-A0E1-679605A2C08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD1CBF2-F2C5-2B48-8F7C-C7A48B481908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1900" yWindow="1900" windowWidth="27760" windowHeight="17140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5731,8 +5731,8 @@
         <v>0.35</v>
       </c>
       <c r="I23" s="25">
-        <f>1500*1.25</f>
-        <v>1875</v>
+        <f>1500</f>
+        <v>1500</v>
       </c>
       <c r="J23" s="25">
         <v>35</v>
